--- a/projects/frontend/assets/generator-template.xlsx
+++ b/projects/frontend/assets/generator-template.xlsx
@@ -680,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="105" customWidth="1" style="19" min="1" max="1"/>
@@ -766,12 +766,22 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" s="19" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>⚠️ Новое: лист «Классы» с количеством учеников, и колонки Вместимость/Этаж/Оборудование у кабинетов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>⚠️ Новое: колонка «Смена» в листе «Классы» (1 — первая смена, 2 — вторая).</t>
         </is>
       </c>
     </row>
@@ -5874,13 +5884,13 @@
           <t>Информатика</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="19" t="n">
         <v>30</v>
       </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>Компьютеры, проектор</t>
         </is>
@@ -5895,13 +5905,13 @@
           <t>Иностранный язык</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="19" t="n">
         <v>28</v>
       </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
         <is>
           <t>Проектор</t>
         </is>
@@ -5916,13 +5926,13 @@
           <t>Физика</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="D4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D4" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>Лабораторные столы, вытяжка</t>
         </is>
@@ -5937,13 +5947,13 @@
           <t>Химия</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="D5" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" s="19" t="inlineStr">
         <is>
           <t>Лабораторные столы, вытяжка</t>
         </is>
@@ -5958,13 +5968,13 @@
           <t>Биология</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="19" t="n">
         <v>28</v>
       </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>Микроскопы</t>
         </is>
@@ -5981,13 +5991,13 @@
           <t>Спортзал</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="19" t="n">
         <v>60</v>
       </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
         <is>
           <t>Маты, снаряды</t>
         </is>
@@ -6004,13 +6014,13 @@
           <t>Мастерская</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Станки, верстаки</t>
         </is>
@@ -6027,13 +6037,13 @@
           <t>Актовый зал</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="19" t="n">
         <v>150</v>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="D9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>Сцена, звук</t>
         </is>
@@ -6083,11 +6093,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="20" min="1" max="1"/>
     <col width="18" customWidth="1" style="20" min="2" max="2"/>
+    <col width="10" customWidth="1" style="20" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6101,445 +6112,582 @@
           <t>Кол-во учеников</t>
         </is>
       </c>
+      <c r="C1" s="38" t="inlineStr">
+        <is>
+          <t>Смена</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>1А</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>1Б</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>1В</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>1Г</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>2А</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>2Б</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>2В</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>2Г</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>3А</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>3Б</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>3В</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>3Г</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>4А</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>4Б</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>4В</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>4Г</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="19" t="n">
         <v>25</v>
       </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>5А</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>5Б</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>5В</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>5Г</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>6А</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>6Б</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>6В</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>6Г</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>7А</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>7Б</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>7В</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>7Г</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>8А</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>8Б</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>8В</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>8Г</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>9А</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>9Б</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>9В</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>9Г</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="19" t="n">
         <v>28</v>
       </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>10А</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="19" t="n">
         <v>22</v>
       </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>10Б</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="19" t="n">
         <v>22</v>
       </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>10В</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" s="19" t="n">
         <v>22</v>
       </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>10Г</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" s="19" t="n">
         <v>22</v>
       </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>11А</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="19" t="n">
         <v>22</v>
       </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>11Б</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" s="19" t="n">
         <v>22</v>
       </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>11В</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" s="19" t="n">
         <v>22</v>
       </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>11Г</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" s="19" t="n">
         <v>22</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
